--- a/model_training-20261019T083032Z-1-001/model_training/model_comparison.xlsx
+++ b/model_training-20261019T083032Z-1-001/model_training/model_comparison.xlsx
@@ -499,76 +499,76 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ARIMA(X)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97.9323</v>
+        <v>98.38760000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>58.614</v>
+        <v>50.7701</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9096</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>126.5195</v>
+        <v>130.2289</v>
       </c>
       <c r="F3" t="n">
-        <v>77.4024</v>
+        <v>83.9739</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8433</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ARIMA(X)</t>
+          <t>Linear Regression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98.38760000000001</v>
+        <v>98.7105</v>
       </c>
       <c r="C4" t="n">
-        <v>50.7701</v>
+        <v>40.7468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9082</v>
       </c>
       <c r="E4" t="n">
-        <v>130.2289</v>
+        <v>130.9178</v>
       </c>
       <c r="F4" t="n">
-        <v>83.9739</v>
+        <v>69.0844</v>
       </c>
       <c r="G4" t="n">
-        <v>0.834</v>
+        <v>0.8322000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Linear Regression</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98.7105</v>
+        <v>99.348</v>
       </c>
       <c r="C5" t="n">
-        <v>40.7468</v>
+        <v>34.0849</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9082</v>
+        <v>0.907</v>
       </c>
       <c r="E5" t="n">
-        <v>130.9178</v>
+        <v>131.8027</v>
       </c>
       <c r="F5" t="n">
-        <v>69.0844</v>
+        <v>59.8887</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="6">
@@ -729,22 +729,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150.471</v>
+        <v>153.8</v>
       </c>
       <c r="C4" t="n">
-        <v>71.61579999999999</v>
+        <v>44.2156</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8101</v>
+        <v>0.8016</v>
       </c>
       <c r="E4" t="n">
-        <v>197.4274</v>
+        <v>204.0431</v>
       </c>
       <c r="F4" t="n">
-        <v>100.2865</v>
+        <v>77.71939999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6887</v>
+        <v>0.6675</v>
       </c>
     </row>
     <row r="5">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.83410000000001</v>
+        <v>35.9077</v>
       </c>
       <c r="D4" t="n">
-        <v>47.596</v>
+        <v>13.7317</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9708</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="5">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>121.5808</v>
+        <v>134.6786</v>
       </c>
       <c r="D10" t="n">
-        <v>69.23099999999999</v>
+        <v>53.6973</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7782</v>
+        <v>0.7278</v>
       </c>
     </row>
     <row r="11">
@@ -1186,10 +1186,10 @@
         <v>79.58663637663905</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6319917549534948</v>
+        <v>0.6319917549534947</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4">
@@ -1222,7 +1222,7 @@
         <v>0.6336391167445193</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5">
@@ -1240,7 +1240,7 @@
         <v>163.7020049499056</v>
       </c>
       <c r="D5" t="n">
-        <v>45.6042875023733</v>
+        <v>45.60428750237331</v>
       </c>
       <c r="E5" t="n">
         <v>0.7796525361596762</v>
@@ -1255,7 +1255,7 @@
         <v>0.6315368897925966</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6">
@@ -1288,7 +1288,7 @@
         <v>0.6314081440888024</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
@@ -1299,29 +1299,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 4, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 4, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>157.9457127122687</v>
+        <v>157.0651997928581</v>
       </c>
       <c r="D7" t="n">
-        <v>72.06097390674829</v>
+        <v>43.91136506978492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7948763465965865</v>
+        <v>0.7971570110336343</v>
       </c>
       <c r="F7" t="n">
-        <v>206.3685456658603</v>
+        <v>207.270526457108</v>
       </c>
       <c r="G7" t="n">
-        <v>100.2638431702223</v>
+        <v>75.42744704358145</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6637739702611307</v>
+        <v>0.660828442167763</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -1332,29 +1332,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 4, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 4, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>161.2209723957208</v>
+        <v>157.1442428475058</v>
       </c>
       <c r="D8" t="n">
-        <v>48.55895050333052</v>
+        <v>43.55661679528577</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7862810008347424</v>
+        <v>0.7969527982115823</v>
       </c>
       <c r="F8" t="n">
-        <v>212.7368793673652</v>
+        <v>207.3728537137906</v>
       </c>
       <c r="G8" t="n">
-        <v>81.80068796345658</v>
+        <v>74.76332037513626</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6427025688702555</v>
+        <v>0.6604934687128773</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -1365,29 +1365,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 6, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 6, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>157.8761731547411</v>
+        <v>156.7740874477931</v>
       </c>
       <c r="D9" t="n">
-        <v>71.01116898484435</v>
+        <v>43.6899881814392</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7950569284910072</v>
+        <v>0.7979082325021921</v>
       </c>
       <c r="F9" t="n">
-        <v>206.2949061421085</v>
+        <v>206.8916914469204</v>
       </c>
       <c r="G9" t="n">
-        <v>98.55115961651767</v>
+        <v>75.6592675884078</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6640138818919494</v>
+        <v>0.6620671386679559</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -1398,29 +1398,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 6, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 6, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160.1695121353772</v>
+        <v>157.6258725877496</v>
       </c>
       <c r="D10" t="n">
-        <v>47.341773245927</v>
+        <v>43.38360789056089</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7890596002303347</v>
+        <v>0.7957062564035661</v>
       </c>
       <c r="F10" t="n">
-        <v>211.3523110983762</v>
+        <v>208.0158129178014</v>
       </c>
       <c r="G10" t="n">
-        <v>79.86852172653803</v>
+        <v>75.10927096806914</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6473382750583823</v>
+        <v>0.6583849260824151</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 8, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 8, 'learning_rate': 0.05, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>157.2307123764418</v>
+        <v>156.4100726329893</v>
       </c>
       <c r="D11" t="n">
-        <v>70.60443577774329</v>
+        <v>43.26392124422653</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7967292809372422</v>
+        <v>0.7988456194604482</v>
       </c>
       <c r="F11" t="n">
-        <v>205.4367775862771</v>
+        <v>206.4121347091966</v>
       </c>
       <c r="G11" t="n">
-        <v>97.85595677153832</v>
+        <v>75.17788543998078</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6668032829905298</v>
+        <v>0.6636319203307455</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1464,29 +1464,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 42, 'max_depth': 8, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
+          <t>{'n_estimators': 800, 'max_depth': 8, 'learning_rate': 0.1, 'subsample': 0.8, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>158.7630976085954</v>
+        <v>156.6620261418115</v>
       </c>
       <c r="D12" t="n">
-        <v>46.88992193184405</v>
+        <v>43.47314196211148</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7927477821067475</v>
+        <v>0.7981970375451959</v>
       </c>
       <c r="F12" t="n">
-        <v>209.4959947799589</v>
+        <v>206.7446227754947</v>
       </c>
       <c r="G12" t="n">
-        <v>79.07418832534785</v>
+        <v>75.5387750354392</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6535059558810339</v>
+        <v>0.6625474061184989</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +1606,7 @@
         <v>0.9779244626575482</v>
       </c>
       <c r="L2" t="n">
-        <v>21.6</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="3">
@@ -1650,7 +1650,7 @@
         <v>0.8277899836431084</v>
       </c>
       <c r="L3" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="4">
@@ -1738,7 +1738,7 @@
         <v>0.9757423106689</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
@@ -1782,7 +1782,7 @@
         <v>0.4251699066091567</v>
       </c>
       <c r="L6" t="n">
-        <v>18.3</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="7">
@@ -1826,7 +1826,7 @@
         <v>0.5410938811268039</v>
       </c>
       <c r="L7" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="8">
@@ -1870,7 +1870,7 @@
         <v>0.6156951997235065</v>
       </c>
       <c r="L8" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="9">
@@ -1914,7 +1914,7 @@
         <v>0.4358561156296438</v>
       </c>
       <c r="L9" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="10">
@@ -1958,7 +1958,7 @@
         <v>0.9115140324514077</v>
       </c>
       <c r="L10" t="n">
-        <v>50.6</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="11">
@@ -2002,7 +2002,7 @@
         <v>0.9204637176277433</v>
       </c>
       <c r="L11" t="n">
-        <v>31.9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -2046,7 +2046,7 @@
         <v>0.8245403995719732</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="13">
@@ -2090,7 +2090,7 @@
         <v>0.410009109854275</v>
       </c>
       <c r="L13" t="n">
-        <v>24.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="14">
@@ -2134,7 +2134,7 @@
         <v>0.4461095557649372</v>
       </c>
       <c r="L14" t="n">
-        <v>41.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="15">
@@ -2178,7 +2178,7 @@
         <v>0.3378797970952282</v>
       </c>
       <c r="L15" t="n">
-        <v>37.8</v>
+        <v>33.1</v>
       </c>
     </row>
   </sheetData>
@@ -2518,7 +2518,7 @@
         <v>0.9937</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7103000283241272</v>
+        <v>0.7771000266075134</v>
       </c>
     </row>
     <row r="3">
@@ -2531,7 +2531,7 @@
         <v>0.0014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2214999943971634</v>
+        <v>0.1018000021576881</v>
       </c>
     </row>
     <row r="4">
@@ -2544,59 +2544,59 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04930000007152557</v>
+        <v>0.07980000227689743</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLANT_ID_4136001</t>
+          <t>MODULE_TEMPERATURE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001</v>
+        <v>0.0022</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007799999788403511</v>
+        <v>0.01579999923706055</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MODULE_TEMPERATURE</t>
+          <t>PLANT_ID_4136001</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004600000102072954</v>
+        <v>0.01209999993443489</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMBIENT_TEMPERATURE</t>
+          <t>HOUR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00279999990016222</v>
+        <v>0.005900000222027302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOUR</t>
+          <t>AMBIENT_TEMPERATURE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002499999944120646</v>
+        <v>0.00419999985024333</v>
       </c>
     </row>
     <row r="9">
@@ -2609,7 +2609,7 @@
         <v>0.0003</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001000000047497451</v>
+        <v>0.003400000045076013</v>
       </c>
     </row>
   </sheetData>
